--- a/cubes/data/materials/windows.xlsx
+++ b/cubes/data/materials/windows.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hannes/Work/elizabeth-homes/src/cubes/data/materials/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hannes/Work/CUBES/cubes/data/materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFDF4B3C-5750-4045-9FC3-B169DCBF4D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3EC8EE5-5915-5241-A23D-DFA443C88EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-4920" yWindow="-21760" windowWidth="25200" windowHeight="18380" xr2:uid="{47704123-5C42-9841-98FC-8623E63A368D}"/>
   </bookViews>
@@ -483,6 +483,9 @@
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
     <col min="3" max="3" width="23.6640625" customWidth="1"/>
+    <col min="8" max="8" width="21.33203125" customWidth="1"/>
+    <col min="9" max="9" width="25.83203125" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
@@ -744,10 +747,10 @@
         <v>0.85</v>
       </c>
       <c r="I8">
-        <v>0.56000000000000005</v>
+        <v>5.6000000000000001E-2</v>
       </c>
       <c r="J8">
-        <v>0.79</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -788,10 +791,10 @@
         <v>0.85</v>
       </c>
       <c r="I9">
-        <v>0.79</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="J9">
-        <v>0.56000000000000005</v>
+        <v>5.6000000000000001E-2</v>
       </c>
       <c r="K9">
         <v>0</v>

--- a/cubes/data/materials/windows.xlsx
+++ b/cubes/data/materials/windows.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hannes/Work/CUBES/cubes/data/materials/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/SSK Harddrive/CUBES/cubes/data/materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3EC8EE5-5915-5241-A23D-DFA443C88EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{143DFFC8-B060-EA4E-8FBA-0D15B65C7986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4920" yWindow="-21760" windowWidth="25200" windowHeight="18380" xr2:uid="{47704123-5C42-9841-98FC-8623E63A368D}"/>
+    <workbookView xWindow="0" yWindow="860" windowWidth="38400" windowHeight="22220" xr2:uid="{47704123-5C42-9841-98FC-8623E63A368D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
   <si>
     <t>Name</t>
   </si>
@@ -117,6 +117,9 @@
   </si>
   <si>
     <t>Clear_3mm_CODE</t>
+  </si>
+  <si>
+    <t>beizaee_glazing</t>
   </si>
 </sst>
 </file>
@@ -181,9 +184,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -221,7 +224,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -327,7 +330,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -469,7 +472,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -477,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21125F1D-BB2D-604B-8747-268ACA9BD3EF}">
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
@@ -856,6 +859,50 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="E11">
+        <v>0.83699999999999997</v>
+      </c>
+      <c r="F11">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G11">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="H11">
+        <v>0.89800000000000002</v>
+      </c>
+      <c r="I11">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="J11">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0.84</v>
+      </c>
+      <c r="M11">
+        <v>0.84</v>
+      </c>
+      <c r="N11">
+        <v>0.9</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
